--- a/artfynd/A 6999-2026 artfynd.xlsx
+++ b/artfynd/A 6999-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131752933</v>
+        <v>131752966</v>
       </c>
       <c r="B2" t="n">
-        <v>57898</v>
+        <v>83107</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495684</v>
+        <v>495642</v>
       </c>
       <c r="R2" t="n">
-        <v>7035365</v>
+        <v>7035357</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,17 +751,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -805,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131752966</v>
+        <v>131752933</v>
       </c>
       <c r="B3" t="n">
-        <v>83106</v>
+        <v>57899</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,26 +807,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -843,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495642</v>
+        <v>495684</v>
       </c>
       <c r="R3" t="n">
-        <v>7035357</v>
+        <v>7035365</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,13 +877,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -929,7 +929,7 @@
         <v>131752965</v>
       </c>
       <c r="B4" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>131752889</v>
       </c>
       <c r="B5" t="n">
-        <v>83240</v>
+        <v>83241</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>131752937</v>
       </c>
       <c r="B6" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>131752936</v>
       </c>
       <c r="B7" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>131752934</v>
       </c>
       <c r="B8" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>131752960</v>
       </c>
       <c r="B9" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>131752954</v>
       </c>
       <c r="B10" t="n">
-        <v>78272</v>
+        <v>78273</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>131752959</v>
       </c>
       <c r="B11" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>131752932</v>
       </c>
       <c r="B12" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131752935</v>
+        <v>131752931</v>
       </c>
       <c r="B13" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495669</v>
+        <v>495680</v>
       </c>
       <c r="R13" t="n">
-        <v>7035364</v>
+        <v>7035331</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2171,14 +2171,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2196,10 +2191,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131752931</v>
+        <v>131752935</v>
       </c>
       <c r="B14" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2229,7 +2224,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2239,10 +2234,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>495680</v>
+        <v>495669</v>
       </c>
       <c r="R14" t="n">
-        <v>7035331</v>
+        <v>7035364</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2279,7 +2274,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2306,9 +2301,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2329,7 +2329,7 @@
         <v>131752964</v>
       </c>
       <c r="B15" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 6999-2026 artfynd.xlsx
+++ b/artfynd/A 6999-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131752966</v>
       </c>
       <c r="B2" t="n">
-        <v>83107</v>
+        <v>83110</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>131752933</v>
       </c>
       <c r="B3" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>131752965</v>
       </c>
       <c r="B4" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>131752889</v>
       </c>
       <c r="B5" t="n">
-        <v>83241</v>
+        <v>83244</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>131752937</v>
       </c>
       <c r="B6" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>131752936</v>
       </c>
       <c r="B7" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>131752934</v>
       </c>
       <c r="B8" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>131752960</v>
       </c>
       <c r="B9" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>131752954</v>
       </c>
       <c r="B10" t="n">
-        <v>78273</v>
+        <v>78276</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>131752959</v>
       </c>
       <c r="B11" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>131752932</v>
       </c>
       <c r="B12" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>131752931</v>
       </c>
       <c r="B13" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>131752935</v>
       </c>
       <c r="B14" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>131752964</v>
       </c>
       <c r="B15" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 6999-2026 artfynd.xlsx
+++ b/artfynd/A 6999-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131752966</v>
+        <v>131752933</v>
       </c>
       <c r="B2" t="n">
-        <v>83110</v>
+        <v>57904</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,26 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495642</v>
+        <v>495684</v>
       </c>
       <c r="R2" t="n">
-        <v>7035357</v>
+        <v>7035365</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,13 +756,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -796,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131752933</v>
+        <v>131752966</v>
       </c>
       <c r="B3" t="n">
-        <v>57902</v>
+        <v>83112</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,31 +816,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -839,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495684</v>
+        <v>495642</v>
       </c>
       <c r="R3" t="n">
-        <v>7035365</v>
+        <v>7035357</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,17 +881,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -929,7 +929,7 @@
         <v>131752965</v>
       </c>
       <c r="B4" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>131752889</v>
       </c>
       <c r="B5" t="n">
-        <v>83244</v>
+        <v>83246</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>131752937</v>
       </c>
       <c r="B6" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>131752936</v>
       </c>
       <c r="B7" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>131752934</v>
       </c>
       <c r="B8" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>131752960</v>
       </c>
       <c r="B9" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>131752954</v>
       </c>
       <c r="B10" t="n">
-        <v>78276</v>
+        <v>78278</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>131752959</v>
       </c>
       <c r="B11" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>131752932</v>
       </c>
       <c r="B12" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>131752931</v>
       </c>
       <c r="B13" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>131752935</v>
       </c>
       <c r="B14" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>131752964</v>
       </c>
       <c r="B15" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 6999-2026 artfynd.xlsx
+++ b/artfynd/A 6999-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131752933</v>
+        <v>131752966</v>
       </c>
       <c r="B2" t="n">
-        <v>57904</v>
+        <v>83115</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495684</v>
+        <v>495642</v>
       </c>
       <c r="R2" t="n">
-        <v>7035365</v>
+        <v>7035357</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,17 +751,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -805,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131752966</v>
+        <v>131752933</v>
       </c>
       <c r="B3" t="n">
-        <v>83112</v>
+        <v>57907</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,26 +807,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -843,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495642</v>
+        <v>495684</v>
       </c>
       <c r="R3" t="n">
-        <v>7035357</v>
+        <v>7035365</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,13 +877,17 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -929,7 +929,7 @@
         <v>131752965</v>
       </c>
       <c r="B4" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>131752889</v>
       </c>
       <c r="B5" t="n">
-        <v>83246</v>
+        <v>83249</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>131752937</v>
       </c>
       <c r="B6" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>131752936</v>
       </c>
       <c r="B7" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>131752934</v>
       </c>
       <c r="B8" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>131752960</v>
       </c>
       <c r="B9" t="n">
-        <v>91858</v>
+        <v>91861</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>131752954</v>
       </c>
       <c r="B10" t="n">
-        <v>78278</v>
+        <v>78281</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>131752959</v>
       </c>
       <c r="B11" t="n">
-        <v>91858</v>
+        <v>91861</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>131752932</v>
       </c>
       <c r="B12" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>131752931</v>
       </c>
       <c r="B13" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>131752935</v>
       </c>
       <c r="B14" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>131752964</v>
       </c>
       <c r="B15" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 6999-2026 artfynd.xlsx
+++ b/artfynd/A 6999-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131752966</v>
       </c>
       <c r="B2" t="n">
-        <v>83115</v>
+        <v>83120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>131752933</v>
       </c>
       <c r="B3" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>131752965</v>
       </c>
       <c r="B4" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>131752889</v>
       </c>
       <c r="B5" t="n">
-        <v>83249</v>
+        <v>83254</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>131752937</v>
       </c>
       <c r="B6" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>131752936</v>
       </c>
       <c r="B7" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>131752934</v>
       </c>
       <c r="B8" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>131752960</v>
       </c>
       <c r="B9" t="n">
-        <v>91861</v>
+        <v>91866</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>131752954</v>
       </c>
       <c r="B10" t="n">
-        <v>78281</v>
+        <v>78286</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>131752959</v>
       </c>
       <c r="B11" t="n">
-        <v>91861</v>
+        <v>91866</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>131752932</v>
       </c>
       <c r="B12" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>131752931</v>
       </c>
       <c r="B13" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>131752935</v>
       </c>
       <c r="B14" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>131752964</v>
       </c>
       <c r="B15" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 6999-2026 artfynd.xlsx
+++ b/artfynd/A 6999-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131752966</v>
       </c>
       <c r="B2" t="n">
-        <v>83120</v>
+        <v>83122</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>131752933</v>
       </c>
       <c r="B3" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>131752965</v>
       </c>
       <c r="B4" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>131752889</v>
       </c>
       <c r="B5" t="n">
-        <v>83254</v>
+        <v>83256</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>131752937</v>
       </c>
       <c r="B6" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1303,10 +1303,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131752936</v>
+        <v>131752934</v>
       </c>
       <c r="B7" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1346,10 +1346,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495537</v>
+        <v>495688</v>
       </c>
       <c r="R7" t="n">
-        <v>7035345</v>
+        <v>7035375</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1413,9 +1413,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1433,10 +1438,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131752934</v>
+        <v>131752936</v>
       </c>
       <c r="B8" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1471,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1476,10 +1481,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495688</v>
+        <v>495537</v>
       </c>
       <c r="R8" t="n">
-        <v>7035375</v>
+        <v>7035345</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1516,7 +1521,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1543,14 +1548,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1571,7 +1571,7 @@
         <v>131752960</v>
       </c>
       <c r="B9" t="n">
-        <v>91866</v>
+        <v>91868</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>131752954</v>
       </c>
       <c r="B10" t="n">
-        <v>78286</v>
+        <v>78288</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>131752959</v>
       </c>
       <c r="B11" t="n">
-        <v>91866</v>
+        <v>91868</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>131752932</v>
       </c>
       <c r="B12" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>131752931</v>
       </c>
       <c r="B13" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>131752935</v>
       </c>
       <c r="B14" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>131752964</v>
       </c>
       <c r="B15" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
